--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96844884</v>
+        <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87195</v>
+        <v>87401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gyllenspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius aureofulvus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720440</v>
+        <v>720289</v>
       </c>
       <c r="R2" t="n">
-        <v>6418164</v>
+        <v>6418205</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844884</t>
+          <t>https://artportalen.se/Sighting/137237205</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96844934</v>
+        <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87309</v>
+        <v>87401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>424</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720538</v>
+        <v>720440</v>
       </c>
       <c r="R3" t="n">
-        <v>6418214</v>
+        <v>6418195</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +887,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844934</t>
+          <t>https://artportalen.se/Sighting/137237223</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96844868</v>
+        <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87146</v>
+        <v>87401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720522</v>
+        <v>720459</v>
       </c>
       <c r="R4" t="n">
-        <v>6418158</v>
+        <v>6418212</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,65 +999,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844868</t>
+          <t>https://artportalen.se/Sighting/137237233</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96844869</v>
+        <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87146</v>
+        <v>87401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3762</v>
+        <v>424</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720537</v>
+        <v>720460</v>
       </c>
       <c r="R5" t="n">
-        <v>6418187</v>
+        <v>6418211</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,49 +1111,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844869</t>
+          <t>https://artportalen.se/Sighting/137237235</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96844870</v>
+        <v>96844884</v>
       </c>
       <c r="B6" t="n">
-        <v>87146</v>
+        <v>87195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius aureofulvus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720458</v>
+        <v>720440</v>
       </c>
       <c r="R6" t="n">
-        <v>6418263</v>
+        <v>6418164</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1184,54 +1224,50 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844870</t>
+          <t>https://artportalen.se/Sighting/96844884</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96844890</v>
+        <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>93215</v>
+        <v>87611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>433</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720466</v>
+        <v>720289</v>
       </c>
       <c r="R7" t="n">
-        <v>6418184</v>
+        <v>6418182</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1291,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,65 +1321,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844890</t>
+          <t>https://artportalen.se/Sighting/137237201</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96844882</v>
+        <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>93194</v>
+        <v>87611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>239737</v>
+        <v>433</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>K.A.Harrison</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720458</v>
+        <v>720416</v>
       </c>
       <c r="R8" t="n">
-        <v>6418165</v>
+        <v>6418207</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1399,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,63 +1429,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844882</t>
+          <t>https://artportalen.se/Sighting/137237225</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95824182</v>
+        <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>75312</v>
+        <v>87611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6000146</v>
+        <v>433</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Grube</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Olarve, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720508</v>
+        <v>720461</v>
       </c>
       <c r="R9" t="n">
-        <v>6418163</v>
+        <v>6418202</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,17 +1507,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Olarve 14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,77 +1531,71 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Död ask</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95824182</t>
+          <t>https://artportalen.se/Sighting/137240060</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96844901</v>
+        <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87346</v>
+        <v>87576</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720516</v>
+        <v>720459</v>
       </c>
       <c r="R10" t="n">
-        <v>6418198</v>
+        <v>6418210</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1570,12 +1619,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,65 +1649,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844901</t>
+          <t>https://artportalen.se/Sighting/137237234</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96844903</v>
+        <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87346</v>
+        <v>87576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720532</v>
+        <v>720468</v>
       </c>
       <c r="R11" t="n">
         <v>6418223</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,12 +1731,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,18 +1761,8462 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137237238</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137240053</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87576</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>449</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720388</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6418177</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240053</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137240057</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87576</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>449</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720448</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6418193</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240057</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137237202</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87497</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>473</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720288</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6418183</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237202</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137237244</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87497</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>473</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720477</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6418234</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237244</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137237224</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93434</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>786</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brandtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum auratile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Britzelm.) Maas Geest.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720407</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6418209</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237224</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137237204</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720289</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6418201</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237204</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137237219</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720436</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6418152</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237219</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137237222</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720443</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6418190</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237222</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137237231</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720450</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6418214</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237231</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137237242</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720484</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6418225</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237242</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137237246</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720462</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6418236</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237246</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137237249</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720402</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6418206</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237249</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137240005</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720488</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6418241</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137240056</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720445</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6418193</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240056</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137240058</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90878</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1595</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brandmusseron</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tricholoma aurantium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.: Fr.) Ricken</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720463</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6418197</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240058</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137237217</v>
+      </c>
+      <c r="B27" t="n">
+        <v>87530</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720437</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6418151</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237217</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137237228</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720420</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6418196</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237228</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137237229</v>
+      </c>
+      <c r="B29" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720432</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6418205</v>
+      </c>
+      <c r="S29" t="n">
+        <v>11</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237229</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137237247</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720447</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6418233</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237247</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>96844934</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720538</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6418214</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844934</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137237200</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720287</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6418171</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237200</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137237251</v>
+      </c>
+      <c r="B33" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720360</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6418205</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237251</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137237252</v>
+      </c>
+      <c r="B34" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720352</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6418213</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237252</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137240048</v>
+      </c>
+      <c r="B35" t="n">
+        <v>87517</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>720319</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6418199</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240048</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137237208</v>
+      </c>
+      <c r="B36" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>720296</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6418194</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237208</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137237209</v>
+      </c>
+      <c r="B37" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>720276</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6418169</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237209</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137237211</v>
+      </c>
+      <c r="B38" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>720321</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6418169</v>
+      </c>
+      <c r="S38" t="n">
+        <v>14</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237211</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137237214</v>
+      </c>
+      <c r="B39" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>720348</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6418164</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237214</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137237220</v>
+      </c>
+      <c r="B40" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>720435</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6418162</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237220</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137237243</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>720481</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6418235</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237243</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137237254</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>720295</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6418213</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237254</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137240006</v>
+      </c>
+      <c r="B43" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>720288</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6418208</v>
+      </c>
+      <c r="S43" t="n">
+        <v>8</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240006</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137240050</v>
+      </c>
+      <c r="B44" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>720316</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6418205</v>
+      </c>
+      <c r="S44" t="n">
+        <v>18</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240050</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137240061</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>720461</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6418202</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240061</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137240067</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>720454</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6418234</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240067</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137240163</v>
+      </c>
+      <c r="B47" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>720324</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6418142</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240163</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137240165</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87378</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>720342</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6418195</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240165</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>96844868</v>
+      </c>
+      <c r="B49" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>720522</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6418158</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844868</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>96844869</v>
+      </c>
+      <c r="B50" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>720537</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6418187</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844869</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>96844870</v>
+      </c>
+      <c r="B51" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>720458</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6418263</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844870</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137237253</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91537</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>720319</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6418220</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237253</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137237230</v>
+      </c>
+      <c r="B53" t="n">
+        <v>93433</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>720448</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6418219</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237230</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137240166</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93433</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>720447</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6418223</v>
+      </c>
+      <c r="S54" t="n">
+        <v>6</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240166</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>96844890</v>
+      </c>
+      <c r="B55" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>720466</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6418184</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844890</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137237221</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93477</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>720437</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6418182</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237221</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137237207</v>
+      </c>
+      <c r="B57" t="n">
+        <v>102515</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>720287</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6418212</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237207</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137237227</v>
+      </c>
+      <c r="B58" t="n">
+        <v>102515</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>720413</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6418197</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237227</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137240066</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92932</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>720458</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6418235</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240066</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>96844882</v>
+      </c>
+      <c r="B60" t="n">
+        <v>93194</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>239737</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knölig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum cumulatum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>720458</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6418165</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844882</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137237206</v>
+      </c>
+      <c r="B61" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>720287</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6418212</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237206</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137237218</v>
+      </c>
+      <c r="B62" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>720435</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6418153</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237218</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>137237245</v>
+      </c>
+      <c r="B63" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>720476</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6418238</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237245</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137240051</v>
+      </c>
+      <c r="B64" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>720344</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6418164</v>
+      </c>
+      <c r="S64" t="n">
+        <v>7</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fast kanske med löv, hassel och ek</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240051</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137240054</v>
+      </c>
+      <c r="B65" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>720419</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6418185</v>
+      </c>
+      <c r="S65" t="n">
+        <v>7</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240054</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137240069</v>
+      </c>
+      <c r="B66" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>720298</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6418217</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240069</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137240167</v>
+      </c>
+      <c r="B67" t="n">
+        <v>87577</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>720459</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6418212</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240167</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137237203</v>
+      </c>
+      <c r="B68" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>720290</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6418190</v>
+      </c>
+      <c r="S68" t="n">
+        <v>6</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237203</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137237210</v>
+      </c>
+      <c r="B69" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>720277</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6418170</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237210</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137237213</v>
+      </c>
+      <c r="B70" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>720329</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6418178</v>
+      </c>
+      <c r="S70" t="n">
+        <v>9</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237213</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137240059</v>
+      </c>
+      <c r="B71" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>720456</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6418178</v>
+      </c>
+      <c r="S71" t="n">
+        <v>7</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240059</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137240064</v>
+      </c>
+      <c r="B72" t="n">
+        <v>87470</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>720520</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6418183</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240064</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137240169</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91643</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>720412</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6418192</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240169</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>95824182</v>
+      </c>
+      <c r="B74" t="n">
+        <v>75312</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6000146</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Coniocarpon fallax</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Grube</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Olarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>720508</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6418163</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Olarve 14</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Död ask</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Raul Vicente, Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95824182</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>96844901</v>
+      </c>
+      <c r="B75" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>720516</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6418198</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96844901</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>96844903</v>
+      </c>
+      <c r="B76" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Olarve Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>720532</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6418223</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/96844903</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137237212</v>
+      </c>
+      <c r="B77" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>720318</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6418170</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237212</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>137237226</v>
+      </c>
+      <c r="B78" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>720418</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6418200</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237226</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137237232</v>
+      </c>
+      <c r="B79" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>720452</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6418213</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237232</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>137237241</v>
+      </c>
+      <c r="B80" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>720506</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6418199</v>
+      </c>
+      <c r="S80" t="n">
+        <v>14</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237241</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137240062</v>
+      </c>
+      <c r="B81" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>720488</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6418202</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240062</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>137240065</v>
+      </c>
+      <c r="B82" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>720466</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6418224</v>
+      </c>
+      <c r="S82" t="n">
+        <v>8</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240065</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>137240068</v>
+      </c>
+      <c r="B83" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>720412</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6418225</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240068</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>137240071</v>
+      </c>
+      <c r="B84" t="n">
+        <v>87554</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle 2, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>720291</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6418230</v>
+      </c>
+      <c r="S84" t="n">
+        <v>8</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240071</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>137237236</v>
+      </c>
+      <c r="B85" t="n">
+        <v>93469</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>720471</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6418212</v>
+      </c>
+      <c r="S85" t="n">
+        <v>7</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237236</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>137237237</v>
+      </c>
+      <c r="B86" t="n">
+        <v>93469</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>720465</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6418215</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237237</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>137240168</v>
+      </c>
+      <c r="B87" t="n">
+        <v>93469</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>720463</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6418214</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240168</t>
         </is>
       </c>
     </row>
@@ -1719,6 +10232,82 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87401</v>
+        <v>87403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237224</v>
       </c>
       <c r="B16" t="n">
-        <v>93434</v>
+        <v>93435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237204</v>
       </c>
       <c r="B17" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237219</v>
       </c>
       <c r="B18" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237222</v>
       </c>
       <c r="B19" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237231</v>
       </c>
       <c r="B20" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237242</v>
       </c>
       <c r="B21" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237246</v>
       </c>
       <c r="B22" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137237249</v>
       </c>
       <c r="B23" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240005</v>
       </c>
       <c r="B24" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240056</v>
       </c>
       <c r="B25" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137240058</v>
       </c>
       <c r="B26" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237217</v>
       </c>
       <c r="B27" t="n">
-        <v>87530</v>
+        <v>87532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237228</v>
       </c>
       <c r="B28" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237229</v>
       </c>
       <c r="B29" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137237247</v>
       </c>
       <c r="B30" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237200</v>
       </c>
       <c r="B32" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237251</v>
       </c>
       <c r="B33" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137237252</v>
       </c>
       <c r="B34" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137240048</v>
       </c>
       <c r="B35" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237208</v>
       </c>
       <c r="B36" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237209</v>
       </c>
       <c r="B37" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237211</v>
       </c>
       <c r="B38" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237214</v>
       </c>
       <c r="B39" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237220</v>
       </c>
       <c r="B40" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237243</v>
       </c>
       <c r="B41" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137237254</v>
       </c>
       <c r="B42" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240006</v>
       </c>
       <c r="B43" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240050</v>
       </c>
       <c r="B44" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240061</v>
       </c>
       <c r="B45" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240067</v>
       </c>
       <c r="B46" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240163</v>
       </c>
       <c r="B47" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137240165</v>
       </c>
       <c r="B48" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>137237253</v>
       </c>
       <c r="B52" t="n">
-        <v>91537</v>
+        <v>91539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>137237230</v>
       </c>
       <c r="B53" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>137240166</v>
       </c>
       <c r="B54" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>137237221</v>
       </c>
       <c r="B56" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>137237207</v>
       </c>
       <c r="B57" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>137237227</v>
       </c>
       <c r="B58" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>137240066</v>
       </c>
       <c r="B59" t="n">
-        <v>92932</v>
+        <v>92934</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>137237206</v>
       </c>
       <c r="B61" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>137237218</v>
       </c>
       <c r="B62" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>137237245</v>
       </c>
       <c r="B63" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>137240051</v>
       </c>
       <c r="B64" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137240054</v>
       </c>
       <c r="B65" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137240069</v>
       </c>
       <c r="B66" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240167</v>
       </c>
       <c r="B67" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>137237203</v>
       </c>
       <c r="B68" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>137237210</v>
       </c>
       <c r="B69" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>137237213</v>
       </c>
       <c r="B70" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>137240059</v>
       </c>
       <c r="B71" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>137240064</v>
       </c>
       <c r="B72" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>137240169</v>
       </c>
       <c r="B73" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>137237212</v>
       </c>
       <c r="B77" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>137237226</v>
       </c>
       <c r="B78" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>137237232</v>
       </c>
       <c r="B79" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>137237241</v>
       </c>
       <c r="B80" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>137240062</v>
       </c>
       <c r="B81" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>137240065</v>
       </c>
       <c r="B82" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>137240068</v>
       </c>
       <c r="B83" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>137240071</v>
       </c>
       <c r="B84" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>137237236</v>
       </c>
       <c r="B85" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>137237237</v>
       </c>
       <c r="B86" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>137240168</v>
       </c>
       <c r="B87" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5912,48 +5912,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>96844868</v>
+        <v>137273868</v>
       </c>
       <c r="B49" t="n">
-        <v>87146</v>
+        <v>87383</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720522</v>
+        <v>720460</v>
       </c>
       <c r="R49" t="n">
-        <v>6418158</v>
+        <v>6418217</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5977,12 +5977,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5997,65 +6007,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844868</t>
+          <t>https://artportalen.se/Sighting/137273868</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96844869</v>
+        <v>137273869</v>
       </c>
       <c r="B50" t="n">
-        <v>87146</v>
+        <v>87383</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720537</v>
+        <v>720399</v>
       </c>
       <c r="R50" t="n">
-        <v>6418187</v>
+        <v>6418214</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6079,12 +6089,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6093,30 +6113,31 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844869</t>
+          <t>https://artportalen.se/Sighting/137273869</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96844870</v>
+        <v>96844868</v>
       </c>
       <c r="B51" t="n">
         <v>87146</v>
@@ -6151,10 +6172,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>720458</v>
+        <v>720522</v>
       </c>
       <c r="R51" t="n">
-        <v>6418263</v>
+        <v>6418158</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6212,16 +6233,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844870</t>
+          <t>https://artportalen.se/Sighting/96844868</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137237253</v>
+        <v>96844869</v>
       </c>
       <c r="B52" t="n">
-        <v>91539</v>
+        <v>87146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6229,37 +6250,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4188</v>
+        <v>3762</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>720319</v>
+        <v>720537</v>
       </c>
       <c r="R52" t="n">
-        <v>6418220</v>
+        <v>6418187</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6283,22 +6304,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6313,65 +6324,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237253</t>
+          <t>https://artportalen.se/Sighting/96844869</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137237230</v>
+        <v>96844870</v>
       </c>
       <c r="B53" t="n">
-        <v>93434</v>
+        <v>87146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>720448</v>
+        <v>720458</v>
       </c>
       <c r="R53" t="n">
-        <v>6418219</v>
+        <v>6418263</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6395,22 +6406,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6425,49 +6426,49 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237230</t>
+          <t>https://artportalen.se/Sighting/96844870</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137240166</v>
+        <v>137237253</v>
       </c>
       <c r="B54" t="n">
-        <v>93434</v>
+        <v>91539</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>4188</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6477,13 +6478,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720447</v>
+        <v>720319</v>
       </c>
       <c r="R54" t="n">
-        <v>6418223</v>
+        <v>6418220</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6512,7 +6513,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6522,7 +6523,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6537,27 +6538,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240166</t>
+          <t>https://artportalen.se/Sighting/137237253</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>96844890</v>
+        <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93215</v>
+        <v>93434</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6565,37 +6566,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720466</v>
+        <v>720448</v>
       </c>
       <c r="R55" t="n">
-        <v>6418184</v>
+        <v>6418219</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6619,12 +6620,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6639,27 +6650,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844890</t>
+          <t>https://artportalen.se/Sighting/137237230</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137237221</v>
+        <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93478</v>
+        <v>93434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6667,21 +6678,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6691,13 +6702,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720437</v>
+        <v>720447</v>
       </c>
       <c r="R56" t="n">
-        <v>6418182</v>
+        <v>6418223</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6726,7 +6737,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6736,7 +6747,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6751,27 +6762,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237221</t>
+          <t>https://artportalen.se/Sighting/137240166</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137237207</v>
+        <v>96844890</v>
       </c>
       <c r="B57" t="n">
-        <v>102517</v>
+        <v>93215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6779,37 +6790,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221235</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>720287</v>
+        <v>720466</v>
       </c>
       <c r="R57" t="n">
-        <v>6418212</v>
+        <v>6418184</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6833,22 +6844,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6863,27 +6864,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237207</t>
+          <t>https://artportalen.se/Sighting/96844890</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137237227</v>
+        <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>102517</v>
+        <v>93478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6891,21 +6892,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6915,13 +6916,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>720413</v>
+        <v>720437</v>
       </c>
       <c r="R58" t="n">
-        <v>6418197</v>
+        <v>6418182</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6950,7 +6951,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6960,7 +6961,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6986,51 +6987,51 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237227</t>
+          <t>https://artportalen.se/Sighting/137237221</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137240066</v>
+        <v>137273867</v>
       </c>
       <c r="B59" t="n">
-        <v>92934</v>
+        <v>58020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>232138</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>720458</v>
+        <v>720444</v>
       </c>
       <c r="R59" t="n">
-        <v>6418235</v>
+        <v>6418205</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7062,7 +7063,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7072,7 +7073,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7087,65 +7088,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240066</t>
+          <t>https://artportalen.se/Sighting/137273867</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>96844882</v>
+        <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>93194</v>
+        <v>102517</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>239737</v>
+        <v>221235</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>K.A.Harrison</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>720458</v>
+        <v>720287</v>
       </c>
       <c r="R60" t="n">
-        <v>6418165</v>
+        <v>6418212</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7169,12 +7170,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7189,49 +7200,49 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844882</t>
+          <t>https://artportalen.se/Sighting/137237207</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137237206</v>
+        <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>87579</v>
+        <v>102517</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248947</v>
+        <v>221235</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7241,13 +7252,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>720287</v>
+        <v>720413</v>
       </c>
       <c r="R61" t="n">
-        <v>6418212</v>
+        <v>6418197</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7276,7 +7287,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7286,7 +7297,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7295,7 +7306,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7313,16 +7323,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237206</t>
+          <t>https://artportalen.se/Sighting/137237227</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137237218</v>
+        <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>87579</v>
+        <v>92934</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7330,37 +7340,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248947</v>
+        <v>232138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>720435</v>
+        <v>720458</v>
       </c>
       <c r="R62" t="n">
-        <v>6418153</v>
+        <v>6418235</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7389,7 +7399,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7399,7 +7409,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7414,65 +7424,65 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237218</t>
+          <t>https://artportalen.se/Sighting/137240066</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137237245</v>
+        <v>96844882</v>
       </c>
       <c r="B63" t="n">
-        <v>87579</v>
+        <v>93194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>248947</v>
+        <v>239737</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Knölig taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Hydnellum cumulatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>K.A.Harrison</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>720476</v>
+        <v>720458</v>
       </c>
       <c r="R63" t="n">
-        <v>6418238</v>
+        <v>6418165</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7496,22 +7506,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7526,24 +7526,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237245</t>
+          <t>https://artportalen.se/Sighting/96844882</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137240051</v>
+        <v>137237206</v>
       </c>
       <c r="B64" t="n">
         <v>87579</v>
@@ -7574,17 +7574,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>720344</v>
+        <v>720287</v>
       </c>
       <c r="R64" t="n">
-        <v>6418164</v>
+        <v>6418212</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7623,12 +7623,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Fast kanske med löv, hassel och ek</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7637,30 +7632,31 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240051</t>
+          <t>https://artportalen.se/Sighting/137237206</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137240054</v>
+        <v>137237218</v>
       </c>
       <c r="B65" t="n">
         <v>87579</v>
@@ -7691,17 +7687,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>720419</v>
+        <v>720435</v>
       </c>
       <c r="R65" t="n">
-        <v>6418185</v>
+        <v>6418153</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7730,7 +7726,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7740,7 +7736,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7755,24 +7751,24 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240054</t>
+          <t>https://artportalen.se/Sighting/137237218</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137240069</v>
+        <v>137237245</v>
       </c>
       <c r="B66" t="n">
         <v>87579</v>
@@ -7803,14 +7799,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>720298</v>
+        <v>720476</v>
       </c>
       <c r="R66" t="n">
-        <v>6418217</v>
+        <v>6418238</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7842,7 +7838,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7852,7 +7848,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7867,24 +7863,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240069</t>
+          <t>https://artportalen.se/Sighting/137237245</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137240167</v>
+        <v>137240051</v>
       </c>
       <c r="B67" t="n">
         <v>87579</v>
@@ -7915,17 +7911,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>720459</v>
+        <v>720344</v>
       </c>
       <c r="R67" t="n">
-        <v>6418212</v>
+        <v>6418164</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7965,6 +7961,11 @@
       <c r="AB67" t="inlineStr">
         <is>
           <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fast kanske med löv, hassel och ek</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7979,27 +7980,27 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240167</t>
+          <t>https://artportalen.se/Sighting/137240051</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137237203</v>
+        <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87472</v>
+        <v>87579</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8007,37 +8008,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>720290</v>
+        <v>720419</v>
       </c>
       <c r="R68" t="n">
-        <v>6418190</v>
+        <v>6418185</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8066,7 +8067,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8076,7 +8077,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8091,27 +8092,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237203</t>
+          <t>https://artportalen.se/Sighting/137240054</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137237210</v>
+        <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87472</v>
+        <v>87579</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8119,34 +8120,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>720277</v>
+        <v>720298</v>
       </c>
       <c r="R69" t="n">
-        <v>6418170</v>
+        <v>6418217</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8178,7 +8179,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8188,7 +8189,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8203,27 +8204,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237210</t>
+          <t>https://artportalen.se/Sighting/137240069</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137237213</v>
+        <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87472</v>
+        <v>87579</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8231,21 +8232,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8255,13 +8256,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>720329</v>
+        <v>720459</v>
       </c>
       <c r="R70" t="n">
-        <v>6418178</v>
+        <v>6418212</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8290,7 +8291,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8300,7 +8301,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8315,24 +8316,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237213</t>
+          <t>https://artportalen.se/Sighting/137240167</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137240059</v>
+        <v>137237203</v>
       </c>
       <c r="B71" t="n">
         <v>87472</v>
@@ -8363,17 +8364,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>720456</v>
+        <v>720290</v>
       </c>
       <c r="R71" t="n">
-        <v>6418178</v>
+        <v>6418190</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8402,7 +8403,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8412,7 +8413,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8427,24 +8428,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240059</t>
+          <t>https://artportalen.se/Sighting/137237203</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137240064</v>
+        <v>137237210</v>
       </c>
       <c r="B72" t="n">
         <v>87472</v>
@@ -8475,14 +8476,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>720520</v>
+        <v>720277</v>
       </c>
       <c r="R72" t="n">
-        <v>6418183</v>
+        <v>6418170</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8514,7 +8515,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8524,7 +8525,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8539,49 +8540,49 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240064</t>
+          <t>https://artportalen.se/Sighting/137237210</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137240169</v>
+        <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>91645</v>
+        <v>87472</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>256756</v>
+        <v>248956</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8591,13 +8592,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>720412</v>
+        <v>720329</v>
       </c>
       <c r="R73" t="n">
-        <v>6418192</v>
+        <v>6418178</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8626,7 +8627,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8636,7 +8637,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8651,63 +8652,65 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240169</t>
+          <t>https://artportalen.se/Sighting/137237213</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>95824182</v>
+        <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>75312</v>
+        <v>87472</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6000146</v>
+        <v>248956</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Coniocarpon fallax</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Grube</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Olarve, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>720508</v>
+        <v>720456</v>
       </c>
       <c r="R74" t="n">
-        <v>6418163</v>
+        <v>6418178</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8731,17 +8734,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Olarve 14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8750,77 +8758,71 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Död ask</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ola Hammarström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Raul Vicente, Ola Hammarström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95824182</t>
+          <t>https://artportalen.se/Sighting/137240059</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>96844901</v>
+        <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87346</v>
+        <v>87472</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>720516</v>
+        <v>720520</v>
       </c>
       <c r="R75" t="n">
-        <v>6418198</v>
+        <v>6418183</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8844,12 +8846,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8864,27 +8876,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844901</t>
+          <t>https://artportalen.se/Sighting/137240064</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>96844903</v>
+        <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>87346</v>
+        <v>91645</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8892,37 +8904,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>256756</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>720532</v>
+        <v>720412</v>
       </c>
       <c r="R76" t="n">
-        <v>6418223</v>
+        <v>6418192</v>
       </c>
       <c r="S76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8946,12 +8958,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8966,65 +8988,63 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844903</t>
+          <t>https://artportalen.se/Sighting/137240169</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137237212</v>
+        <v>95824182</v>
       </c>
       <c r="B77" t="n">
-        <v>87556</v>
+        <v>75312</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
+        <v>6000146</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Coniocarpon fallax</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Ach.) Grube</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>720318</v>
+        <v>720508</v>
       </c>
       <c r="R77" t="n">
-        <v>6418170</v>
+        <v>6418163</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9048,22 +9068,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:06</t>
+          <t>2021-07-15</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Olarve 14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9076,30 +9091,35 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Död ask</t>
+        </is>
+      </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237212</t>
+          <t>https://artportalen.se/Sighting/95824182</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137237226</v>
+        <v>96844901</v>
       </c>
       <c r="B78" t="n">
-        <v>87556</v>
+        <v>87346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9127,17 +9147,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>720418</v>
+        <v>720516</v>
       </c>
       <c r="R78" t="n">
-        <v>6418200</v>
+        <v>6418198</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9161,22 +9181,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9185,34 +9195,33 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237226</t>
+          <t>https://artportalen.se/Sighting/96844901</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137237232</v>
+        <v>96844903</v>
       </c>
       <c r="B79" t="n">
-        <v>87556</v>
+        <v>87346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9240,17 +9249,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>720452</v>
+        <v>720532</v>
       </c>
       <c r="R79" t="n">
-        <v>6418213</v>
+        <v>6418223</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9274,22 +9283,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9298,31 +9297,30 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237232</t>
+          <t>https://artportalen.se/Sighting/96844903</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>137237241</v>
+        <v>137237212</v>
       </c>
       <c r="B80" t="n">
         <v>87556</v>
@@ -9357,13 +9355,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>720506</v>
+        <v>720318</v>
       </c>
       <c r="R80" t="n">
-        <v>6418199</v>
+        <v>6418170</v>
       </c>
       <c r="S80" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9392,7 +9390,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9402,7 +9400,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9429,13 +9427,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237241</t>
+          <t>https://artportalen.se/Sighting/137237212</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>137240062</v>
+        <v>137237226</v>
       </c>
       <c r="B81" t="n">
         <v>87556</v>
@@ -9466,14 +9464,14 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>720488</v>
+        <v>720418</v>
       </c>
       <c r="R81" t="n">
-        <v>6418202</v>
+        <v>6418200</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9505,7 +9503,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9515,7 +9513,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9524,30 +9522,31 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240062</t>
+          <t>https://artportalen.se/Sighting/137237226</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137240065</v>
+        <v>137237232</v>
       </c>
       <c r="B82" t="n">
         <v>87556</v>
@@ -9578,17 +9577,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>720466</v>
+        <v>720452</v>
       </c>
       <c r="R82" t="n">
-        <v>6418224</v>
+        <v>6418213</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9617,7 +9616,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9627,7 +9626,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9636,30 +9635,31 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240065</t>
+          <t>https://artportalen.se/Sighting/137237232</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>137240068</v>
+        <v>137237241</v>
       </c>
       <c r="B83" t="n">
         <v>87556</v>
@@ -9690,17 +9690,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>720412</v>
+        <v>720506</v>
       </c>
       <c r="R83" t="n">
-        <v>6418225</v>
+        <v>6418199</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9748,30 +9748,31 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240068</t>
+          <t>https://artportalen.se/Sighting/137237241</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>137240071</v>
+        <v>137240062</v>
       </c>
       <c r="B84" t="n">
         <v>87556</v>
@@ -9806,13 +9807,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>720291</v>
+        <v>720488</v>
       </c>
       <c r="R84" t="n">
-        <v>6418230</v>
+        <v>6418202</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9841,7 +9842,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9851,7 +9852,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9877,16 +9878,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240071</t>
+          <t>https://artportalen.se/Sighting/137240062</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>137237236</v>
+        <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>93470</v>
+        <v>87556</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9894,37 +9895,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6332770</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>720471</v>
+        <v>720466</v>
       </c>
       <c r="R85" t="n">
-        <v>6418212</v>
+        <v>6418224</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9953,7 +9954,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9963,7 +9964,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9972,34 +9973,33 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237236</t>
+          <t>https://artportalen.se/Sighting/137240065</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>137237237</v>
+        <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>93470</v>
+        <v>87556</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10007,34 +10007,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6332770</v>
+        <v>6003295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>720465</v>
+        <v>720412</v>
       </c>
       <c r="R86" t="n">
-        <v>6418215</v>
+        <v>6418225</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10085,34 +10085,33 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237237</t>
+          <t>https://artportalen.se/Sighting/137240068</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>137240168</v>
+        <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>93470</v>
+        <v>87556</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10120,37 +10119,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6332770</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>720463</v>
+        <v>720291</v>
       </c>
       <c r="R87" t="n">
-        <v>6418214</v>
+        <v>6418230</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10179,7 +10178,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10189,7 +10188,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10198,23 +10197,469 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137240071</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>137273866</v>
+      </c>
+      <c r="B88" t="n">
+        <v>93459</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>720448</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6418210</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Margaret Rainey</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137273866</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>137237236</v>
+      </c>
+      <c r="B89" t="n">
+        <v>93470</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>720471</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6418212</v>
+      </c>
+      <c r="S89" t="n">
+        <v>7</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237236</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>137237237</v>
+      </c>
+      <c r="B90" t="n">
+        <v>93470</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>720465</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6418215</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137237237</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>137240168</v>
+      </c>
+      <c r="B91" t="n">
+        <v>93470</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Hangvar Kassle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>720463</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6418214</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137240168</t>
         </is>
@@ -10308,6 +10753,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237224</v>
       </c>
       <c r="B16" t="n">
-        <v>93435</v>
+        <v>93438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237204</v>
       </c>
       <c r="B17" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237219</v>
       </c>
       <c r="B18" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237222</v>
       </c>
       <c r="B19" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237231</v>
       </c>
       <c r="B20" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237242</v>
       </c>
       <c r="B21" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237246</v>
       </c>
       <c r="B22" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137237249</v>
       </c>
       <c r="B23" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240005</v>
       </c>
       <c r="B24" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240056</v>
       </c>
       <c r="B25" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137240058</v>
       </c>
       <c r="B26" t="n">
-        <v>90880</v>
+        <v>90883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237217</v>
       </c>
       <c r="B27" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237228</v>
       </c>
       <c r="B28" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237229</v>
       </c>
       <c r="B29" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>137237247</v>
       </c>
       <c r="B30" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237200</v>
       </c>
       <c r="B32" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237251</v>
       </c>
       <c r="B33" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137237252</v>
       </c>
       <c r="B34" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137240048</v>
       </c>
       <c r="B35" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237208</v>
       </c>
       <c r="B36" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237209</v>
       </c>
       <c r="B37" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237211</v>
       </c>
       <c r="B38" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237214</v>
       </c>
       <c r="B39" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237220</v>
       </c>
       <c r="B40" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237243</v>
       </c>
       <c r="B41" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137237254</v>
       </c>
       <c r="B42" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240006</v>
       </c>
       <c r="B43" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240050</v>
       </c>
       <c r="B44" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240061</v>
       </c>
       <c r="B45" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240067</v>
       </c>
       <c r="B46" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240163</v>
       </c>
       <c r="B47" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137240165</v>
       </c>
       <c r="B48" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237253</v>
       </c>
       <c r="B54" t="n">
-        <v>91539</v>
+        <v>91542</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92934</v>
+        <v>92937</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91645</v>
+        <v>91648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9775,7 +9775,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,32 +2226,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137237224</v>
+        <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>93438</v>
+        <v>90893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>786</v>
+        <v>1595</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandtaggsvamp</t>
+          <t>Brandmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum auratile</t>
+          <t>Tricholoma aurantium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Britzelm.) Maas Geest.</t>
+          <t>(Schaeff.: Fr.) Ricken</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720407</v>
+        <v>720289</v>
       </c>
       <c r="R16" t="n">
-        <v>6418209</v>
+        <v>6418201</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,16 +2332,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237224</t>
+          <t>https://artportalen.se/Sighting/137237204</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137237204</v>
+        <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720289</v>
+        <v>720436</v>
       </c>
       <c r="R17" t="n">
-        <v>6418201</v>
+        <v>6418152</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2444,16 +2444,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237204</t>
+          <t>https://artportalen.se/Sighting/137237219</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137237219</v>
+        <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720436</v>
+        <v>720443</v>
       </c>
       <c r="R18" t="n">
-        <v>6418152</v>
+        <v>6418190</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,16 +2556,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237219</t>
+          <t>https://artportalen.se/Sighting/137237222</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137237222</v>
+        <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720443</v>
+        <v>720450</v>
       </c>
       <c r="R19" t="n">
-        <v>6418190</v>
+        <v>6418214</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,16 +2668,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237222</t>
+          <t>https://artportalen.se/Sighting/137237231</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137237231</v>
+        <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,13 +2709,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720450</v>
+        <v>720484</v>
       </c>
       <c r="R20" t="n">
-        <v>6418214</v>
+        <v>6418225</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,16 +2780,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237231</t>
+          <t>https://artportalen.se/Sighting/137237242</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137237242</v>
+        <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720484</v>
+        <v>720462</v>
       </c>
       <c r="R21" t="n">
-        <v>6418225</v>
+        <v>6418236</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,16 +2892,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237242</t>
+          <t>https://artportalen.se/Sighting/137237246</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137237246</v>
+        <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720462</v>
+        <v>720402</v>
       </c>
       <c r="R22" t="n">
-        <v>6418236</v>
+        <v>6418206</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3004,16 +3004,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237246</t>
+          <t>https://artportalen.se/Sighting/137237249</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137237249</v>
+        <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720402</v>
+        <v>720488</v>
       </c>
       <c r="R23" t="n">
-        <v>6418206</v>
+        <v>6418241</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,27 +3105,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237249</t>
+          <t>https://artportalen.se/Sighting/137240005</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137240005</v>
+        <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,14 +3153,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720488</v>
+        <v>720445</v>
       </c>
       <c r="R24" t="n">
-        <v>6418241</v>
+        <v>6418193</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3217,27 +3217,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240005</t>
+          <t>https://artportalen.se/Sighting/137240056</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137240056</v>
+        <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90883</v>
+        <v>90893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720445</v>
+        <v>720463</v>
       </c>
       <c r="R25" t="n">
-        <v>6418193</v>
+        <v>6418197</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3340,54 +3340,54 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240056</t>
+          <t>https://artportalen.se/Sighting/137240058</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137240058</v>
+        <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>90883</v>
+        <v>87545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1595</v>
+        <v>1988</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brandmusseron</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma aurantium</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.: Fr.) Ricken</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720463</v>
+        <v>720437</v>
       </c>
       <c r="R26" t="n">
-        <v>6418197</v>
+        <v>6418151</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3441,49 +3441,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240058</t>
+          <t>https://artportalen.se/Sighting/137237217</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137237217</v>
+        <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>87535</v>
+        <v>96616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1988</v>
+        <v>2812</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720437</v>
+        <v>720420</v>
       </c>
       <c r="R27" t="n">
-        <v>6418151</v>
+        <v>6418196</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,16 +3564,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237217</t>
+          <t>https://artportalen.se/Sighting/137237228</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137237228</v>
+        <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,13 +3605,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720420</v>
+        <v>720432</v>
       </c>
       <c r="R28" t="n">
-        <v>6418196</v>
+        <v>6418205</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3676,16 +3676,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237228</t>
+          <t>https://artportalen.se/Sighting/137237229</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137237229</v>
+        <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3717,13 +3717,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720432</v>
+        <v>720447</v>
       </c>
       <c r="R29" t="n">
-        <v>6418205</v>
+        <v>6418233</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3788,16 +3788,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237229</t>
+          <t>https://artportalen.se/Sighting/137237247</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137237247</v>
+        <v>96844934</v>
       </c>
       <c r="B30" t="n">
-        <v>96606</v>
+        <v>87309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3805,37 +3805,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2812</v>
+        <v>3674</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720447</v>
+        <v>720538</v>
       </c>
       <c r="R30" t="n">
-        <v>6418233</v>
+        <v>6418214</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3859,22 +3859,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3889,27 +3879,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237247</t>
+          <t>https://artportalen.se/Sighting/96844934</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96844934</v>
+        <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87309</v>
+        <v>87532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3937,17 +3927,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720538</v>
+        <v>720287</v>
       </c>
       <c r="R31" t="n">
-        <v>6418214</v>
+        <v>6418171</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3971,12 +3961,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3991,27 +3991,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844934</t>
+          <t>https://artportalen.se/Sighting/137237200</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137237200</v>
+        <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720287</v>
+        <v>720360</v>
       </c>
       <c r="R32" t="n">
-        <v>6418171</v>
+        <v>6418205</v>
       </c>
       <c r="S32" t="n">
         <v>6</v>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,16 +4114,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237200</t>
+          <t>https://artportalen.se/Sighting/137237251</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137237251</v>
+        <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>720360</v>
+        <v>720352</v>
       </c>
       <c r="R33" t="n">
-        <v>6418205</v>
+        <v>6418213</v>
       </c>
       <c r="S33" t="n">
         <v>6</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4226,16 +4226,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237251</t>
+          <t>https://artportalen.se/Sighting/137237252</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137237252</v>
+        <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,17 +4263,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720352</v>
+        <v>720319</v>
       </c>
       <c r="R34" t="n">
-        <v>6418213</v>
+        <v>6418199</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4327,62 +4327,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237252</t>
+          <t>https://artportalen.se/Sighting/137240048</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137240048</v>
+        <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87522</v>
+        <v>87393</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720319</v>
+        <v>720296</v>
       </c>
       <c r="R35" t="n">
-        <v>6418199</v>
+        <v>6418194</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4439,27 +4439,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240048</t>
+          <t>https://artportalen.se/Sighting/137237208</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137237208</v>
+        <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720296</v>
+        <v>720276</v>
       </c>
       <c r="R36" t="n">
-        <v>6418194</v>
+        <v>6418169</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4562,16 +4562,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237208</t>
+          <t>https://artportalen.se/Sighting/137237209</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137237209</v>
+        <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720276</v>
+        <v>720321</v>
       </c>
       <c r="R37" t="n">
         <v>6418169</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4674,16 +4674,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237209</t>
+          <t>https://artportalen.se/Sighting/137237211</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137237211</v>
+        <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720321</v>
+        <v>720348</v>
       </c>
       <c r="R38" t="n">
-        <v>6418169</v>
+        <v>6418164</v>
       </c>
       <c r="S38" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4786,16 +4786,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237211</t>
+          <t>https://artportalen.se/Sighting/137237214</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137237214</v>
+        <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720348</v>
+        <v>720435</v>
       </c>
       <c r="R39" t="n">
-        <v>6418164</v>
+        <v>6418162</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,16 +4898,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237214</t>
+          <t>https://artportalen.se/Sighting/137237220</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137237220</v>
+        <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720435</v>
+        <v>720481</v>
       </c>
       <c r="R40" t="n">
-        <v>6418162</v>
+        <v>6418235</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5010,16 +5010,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237220</t>
+          <t>https://artportalen.se/Sighting/137237243</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137237243</v>
+        <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720481</v>
+        <v>720295</v>
       </c>
       <c r="R41" t="n">
-        <v>6418235</v>
+        <v>6418213</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5122,16 +5122,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237243</t>
+          <t>https://artportalen.se/Sighting/137237254</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137237254</v>
+        <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720295</v>
+        <v>720288</v>
       </c>
       <c r="R42" t="n">
-        <v>6418213</v>
+        <v>6418208</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5223,27 +5223,27 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237254</t>
+          <t>https://artportalen.se/Sighting/137240006</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137240006</v>
+        <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5271,17 +5271,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Hangvar Kassle 2, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720288</v>
+        <v>720316</v>
       </c>
       <c r="R43" t="n">
-        <v>6418208</v>
+        <v>6418205</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5335,27 +5335,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens, Margaret Rainey, Pia Rydh, Ulla Sebestyen, Anna Helmersson, Martin Axegård</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240006</t>
+          <t>https://artportalen.se/Sighting/137240050</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137240050</v>
+        <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>720316</v>
+        <v>720461</v>
       </c>
       <c r="R44" t="n">
-        <v>6418205</v>
+        <v>6418202</v>
       </c>
       <c r="S44" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5458,16 +5458,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240050</t>
+          <t>https://artportalen.se/Sighting/137240061</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137240061</v>
+        <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720461</v>
+        <v>720454</v>
       </c>
       <c r="R45" t="n">
-        <v>6418202</v>
+        <v>6418234</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5570,16 +5570,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240061</t>
+          <t>https://artportalen.se/Sighting/137240067</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137240067</v>
+        <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5607,14 +5607,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hangvar Kassle 2, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720454</v>
+        <v>720324</v>
       </c>
       <c r="R46" t="n">
-        <v>6418234</v>
+        <v>6418142</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5671,27 +5671,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240067</t>
+          <t>https://artportalen.se/Sighting/137240163</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137240163</v>
+        <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5723,13 +5723,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720324</v>
+        <v>720342</v>
       </c>
       <c r="R47" t="n">
-        <v>6418142</v>
+        <v>6418195</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5794,16 +5794,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240163</t>
+          <t>https://artportalen.se/Sighting/137240165</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137240165</v>
+        <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5835,13 +5835,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720342</v>
+        <v>720460</v>
       </c>
       <c r="R48" t="n">
-        <v>6418195</v>
+        <v>6418217</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5895,27 +5895,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Pia Rydh, Margaret Rainey, Anna Helmersson, Martin Axegård, Bo karlstens</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137240165</t>
+          <t>https://artportalen.se/Sighting/137273868</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137273868</v>
+        <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5947,10 +5947,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720460</v>
+        <v>720399</v>
       </c>
       <c r="R49" t="n">
-        <v>6418217</v>
+        <v>6418214</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6001,6 +6001,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6018,54 +6019,54 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273868</t>
+          <t>https://artportalen.se/Sighting/137273869</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137273869</v>
+        <v>96844868</v>
       </c>
       <c r="B50" t="n">
-        <v>87383</v>
+        <v>87146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Hangvar Kassle, Gtl</t>
+          <t>Olarve Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720399</v>
+        <v>720522</v>
       </c>
       <c r="R50" t="n">
-        <v>6418214</v>
+        <v>6418158</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6089,22 +6090,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6113,31 +6104,30 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Margaret Rainey</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137273869</t>
+          <t>https://artportalen.se/Sighting/96844868</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96844868</v>
+        <v>96844869</v>
       </c>
       <c r="B51" t="n">
         <v>87146</v>
@@ -6172,10 +6162,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>720522</v>
+        <v>720537</v>
       </c>
       <c r="R51" t="n">
-        <v>6418158</v>
+        <v>6418187</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6233,13 +6223,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844868</t>
+          <t>https://artportalen.se/Sighting/96844869</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>96844869</v>
+        <v>96844870</v>
       </c>
       <c r="B52" t="n">
         <v>87146</v>
@@ -6274,10 +6264,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>720537</v>
+        <v>720458</v>
       </c>
       <c r="R52" t="n">
-        <v>6418187</v>
+        <v>6418263</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6335,16 +6325,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844869</t>
+          <t>https://artportalen.se/Sighting/96844870</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>96844870</v>
+        <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>87146</v>
+        <v>91552</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6352,37 +6342,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3762</v>
+        <v>4188</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Olarve Kassle, Gtl</t>
+          <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>720458</v>
+        <v>720319</v>
       </c>
       <c r="R53" t="n">
-        <v>6418263</v>
+        <v>6418220</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6406,12 +6396,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6426,65 +6426,68 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96844870</t>
+          <t>https://artportalen.se/Sighting/137237253</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137237253</v>
+        <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>91542</v>
+        <v>93447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4188</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hangvar Kassle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720319</v>
+        <v>720407</v>
       </c>
       <c r="R54" t="n">
-        <v>6418220</v>
+        <v>6418209</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6513,7 +6516,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6523,7 +6526,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6532,6 +6535,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6549,7 +6553,7 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137237253</t>
+          <t>https://artportalen.se/Sighting/137237224</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6670,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6884,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6996,7 +7000,7 @@
         <v>137273867</v>
       </c>
       <c r="B59" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7108,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7220,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7332,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92937</v>
+        <v>92947</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7546,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7659,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7771,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7883,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8000,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8112,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8224,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8336,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8448,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8560,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8672,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8784,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8896,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91648</v>
+        <v>91658</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9323,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9436,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9549,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9662,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9775,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9887,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9999,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10111,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10223,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93459</v>
+        <v>93469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10331,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93473</v>
+        <v>93483</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10444,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93473</v>
+        <v>93483</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10557,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93473</v>
+        <v>93483</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90893</v>
+        <v>90894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92947</v>
+        <v>92948</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91658</v>
+        <v>91659</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93483</v>
+        <v>93484</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93483</v>
+        <v>93484</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93483</v>
+        <v>93484</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90894</v>
+        <v>90897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>137273867</v>
       </c>
       <c r="B59" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92948</v>
+        <v>92951</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91659</v>
+        <v>91662</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93470</v>
+        <v>93475</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93484</v>
+        <v>93489</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93484</v>
+        <v>93489</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93484</v>
+        <v>93489</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92951</v>
+        <v>92953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91662</v>
+        <v>91664</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93475</v>
+        <v>93477</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93489</v>
+        <v>93491</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93489</v>
+        <v>93491</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93489</v>
+        <v>93491</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90897</v>
+        <v>90902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>137273867</v>
       </c>
       <c r="B59" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92953</v>
+        <v>92958</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91664</v>
+        <v>91669</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93477</v>
+        <v>93483</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93491</v>
+        <v>93497</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93491</v>
+        <v>93497</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93491</v>
+        <v>93497</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90902</v>
+        <v>90913</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92958</v>
+        <v>92970</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91669</v>
+        <v>91681</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93483</v>
+        <v>93495</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93497</v>
+        <v>93509</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93497</v>
+        <v>93509</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93497</v>
+        <v>93509</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90913</v>
+        <v>90914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93473</v>
+        <v>93474</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91681</v>
+        <v>91682</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93495</v>
+        <v>93496</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93509</v>
+        <v>93510</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93509</v>
+        <v>93510</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93509</v>
+        <v>93510</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90914</v>
+        <v>90917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93474</v>
+        <v>93477</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91682</v>
+        <v>91685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93496</v>
+        <v>93499</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93510</v>
+        <v>93513</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93510</v>
+        <v>93513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93510</v>
+        <v>93513</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 6159-2023 artfynd.xlsx
+++ b/artfynd/A 6159-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137237205</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137237223</v>
       </c>
       <c r="B3" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137237233</v>
       </c>
       <c r="B4" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137237235</v>
       </c>
       <c r="B5" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>137237201</v>
       </c>
       <c r="B7" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137237225</v>
       </c>
       <c r="B8" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>137240060</v>
       </c>
       <c r="B9" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137237234</v>
       </c>
       <c r="B10" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137237238</v>
       </c>
       <c r="B11" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137240053</v>
       </c>
       <c r="B12" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>137240057</v>
       </c>
       <c r="B13" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>137237202</v>
       </c>
       <c r="B14" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>137237244</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>137237204</v>
       </c>
       <c r="B16" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>137237219</v>
       </c>
       <c r="B17" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>137237222</v>
       </c>
       <c r="B18" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>137237231</v>
       </c>
       <c r="B19" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>137237242</v>
       </c>
       <c r="B20" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>137237246</v>
       </c>
       <c r="B21" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>137237249</v>
       </c>
       <c r="B22" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>137240005</v>
       </c>
       <c r="B23" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>137240056</v>
       </c>
       <c r="B24" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>137240058</v>
       </c>
       <c r="B25" t="n">
-        <v>90917</v>
+        <v>90921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>137237217</v>
       </c>
       <c r="B26" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>137237228</v>
       </c>
       <c r="B27" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>137237229</v>
       </c>
       <c r="B28" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>137237247</v>
       </c>
       <c r="B29" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>137237200</v>
       </c>
       <c r="B31" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>137237251</v>
       </c>
       <c r="B32" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137237252</v>
       </c>
       <c r="B33" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         <v>137240048</v>
       </c>
       <c r="B34" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>137237208</v>
       </c>
       <c r="B35" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>137237209</v>
       </c>
       <c r="B36" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137237211</v>
       </c>
       <c r="B37" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>137237214</v>
       </c>
       <c r="B38" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>137237220</v>
       </c>
       <c r="B39" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137237243</v>
       </c>
       <c r="B40" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>137237254</v>
       </c>
       <c r="B41" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137240006</v>
       </c>
       <c r="B42" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>137240050</v>
       </c>
       <c r="B43" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>137240061</v>
       </c>
       <c r="B44" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>137240067</v>
       </c>
       <c r="B45" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137240163</v>
       </c>
       <c r="B46" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>137240165</v>
       </c>
       <c r="B47" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>137273868</v>
       </c>
       <c r="B48" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>137273869</v>
       </c>
       <c r="B49" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>137237253</v>
       </c>
       <c r="B53" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>137237224</v>
       </c>
       <c r="B54" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>137237230</v>
       </c>
       <c r="B55" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>137240166</v>
       </c>
       <c r="B56" t="n">
-        <v>93477</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>137237221</v>
       </c>
       <c r="B58" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>137273867</v>
       </c>
       <c r="B59" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>137237207</v>
       </c>
       <c r="B60" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137237227</v>
       </c>
       <c r="B61" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>137240066</v>
       </c>
       <c r="B62" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>137237206</v>
       </c>
       <c r="B64" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>137237218</v>
       </c>
       <c r="B65" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>137237245</v>
       </c>
       <c r="B66" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>137240051</v>
       </c>
       <c r="B67" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>137240054</v>
       </c>
       <c r="B68" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>137240069</v>
       </c>
       <c r="B69" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>137240167</v>
       </c>
       <c r="B70" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>137237203</v>
       </c>
       <c r="B71" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137237210</v>
       </c>
       <c r="B72" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>137237213</v>
       </c>
       <c r="B73" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>137240059</v>
       </c>
       <c r="B74" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>137240064</v>
       </c>
       <c r="B75" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>137240169</v>
       </c>
       <c r="B76" t="n">
-        <v>91685</v>
+        <v>91689</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137237212</v>
       </c>
       <c r="B80" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>137237226</v>
       </c>
       <c r="B81" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>137237232</v>
       </c>
       <c r="B82" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>137237241</v>
       </c>
       <c r="B83" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>137240062</v>
       </c>
       <c r="B84" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>137240065</v>
       </c>
       <c r="B85" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>137240068</v>
       </c>
       <c r="B86" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>137240071</v>
       </c>
       <c r="B87" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>137273866</v>
       </c>
       <c r="B88" t="n">
-        <v>93499</v>
+        <v>93503</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>137237236</v>
       </c>
       <c r="B89" t="n">
-        <v>93513</v>
+        <v>93517</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>137237237</v>
       </c>
       <c r="B90" t="n">
-        <v>93513</v>
+        <v>93517</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>137240168</v>
       </c>
       <c r="B91" t="n">
-        <v>93513</v>
+        <v>93517</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
